--- a/data_extactor/batch_10_fa/trimmed/batch_0046_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0046_fa_trim.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | نظارت | نگارش | یادگیری فعال | علوم پایه | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | نظارت | نگارش | یادگیری فعال | علوم | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | روان‌شناسی | زیست‌شناسی | درمان و مشاوره | آموزش و تدریس | شیمی</t>
+          <t>پزشکی و دندان‌پزشکی | روان‌شناسی | زیست‌شناسی | درمان و مشاوره | آموزش و پرورش | شیمی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | بیان شفاهی | درک شفاهی | درک کتبی | مرتب‌سازی اطلاعات</t>
+          <t>استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | بیان شفاهی | درک شفاهی | درک کتبی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>متخصصان روان‌شناسی اعصاب بالینی | پزشکان طب اورژانس | پزشکان خانواده | متخصصان بیماری‌های داخلی | روان‌شناسان اعصاب | متخصصان طب فیزیکی و توانبخشی | روان‌پزشکان</t>
+          <t>متخصصان عصب‌روان‌شناسی بالینی | پزشکان طب اورژانس | پزشکان عمومی و خانواده | پزشکان متخصص بیماری‌های داخلی | متخصصان عصب‌روان‌شناسی | متخصصان طب فیزیکی و توانبخشی | روان‌پزشکان</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,12 +565,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | شنیدن فعال | یادگیری فعال | سخن گفتن | نگارش | نظارت | علوم پایه | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | یادگیری فعال | سخن گفتن | نگارش | نظارت | علوم | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | روان‌شناسی | خدمات مشتریان و خدمات فردی | درمان و مشاوره | آموزش و تدریس</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | روان‌شناسی | خدمات مشتری و شخصی | درمان و مشاوره | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>پزشکان طب اورژانس | پزشکان خانواده | ماماها | پرستاران پیشرفته بالینی | متخصصان عمومی کودکان | پرستاران رسمی | متخصصان اورولوژی</t>
+          <t>پزشکان طب اورژانس | پزشکان عمومی و خانواده | ماماهای پرستار | پرستاران بالینی پیشرفته | متخصصان عمومی کودکان | پرستاران | متخصصان اورولوژی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,12 +622,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | درک مطلب | شنیدن فعال | نظارت | یادگیری فعال | علوم پایه | نگارش | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | درک مطلب | گوش دادن فعال | نظارت | یادگیری فعال | علوم | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | درمان و مشاوره | زیست‌شناسی | روان‌شناسی | خدمات مشتریان و خدمات فردی | آموزش و تدریس</t>
+          <t>پزشکی و دندان‌پزشکی | درمان و مشاوره | زیست‌شناسی | روان‌شناسی | خدمات مشتری و شخصی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>پرستاران متخصص بالینی | پزشکان طب اورژانس | پزشکان خانواده | ماماها | متخصصان زنان و زایمان | جراحان کودکان | دستیاران پزشک</t>
+          <t>پرستاران متخصص بالینی | پزشکان طب اورژانس | پزشکان عمومی و خانواده | ماماهای پرستار | متخصصان زنان و زایمان | جراحان اطفال | دستیاران پزشک</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | نگارش | تفکر انتقادی | علوم پایه | شنیدن فعال | یادگیری فعال | سخن گفتن | نظارت | راهبردهای یادگیری | ریاضیات</t>
+          <t>درک مطلب | نگارش | تفکر انتقادی | علوم | گوش دادن فعال | یادگیری فعال | سخن گفتن | نظارت | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | آموزش و تدریس | خدمات مشتریان و خدمات فردی | شیمی | رایانه و الکترونیک</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | آموزش و پرورش | خدمات مشتری و شخصی | شیمی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>استدلال استقرایی | حساسیت به مسئله | بیان کتبی | درک شفاهی | درک کتبی | استدلال قیاسی | دید نزدیک</t>
+          <t>استدلال استقرایی | حساسیت به مسئله | بیان کتبی | درک شفاهی | درک کتبی | استدلال قیاسی | بینایی نزدیک</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>کارشناسان ژنتیک سلولی | کارشناسان سیتوتکنولوژی | کارشناسان بافت‌شناسی | دانشمندان علوم پزشکی، غیر از همه‌گیرشناسان | کاردان‌های آزمایشگاه پزشکی و بالینی | کارشناسان آزمایشگاه پزشکی و بالینی | متخصصان رادیولوژی</t>
+          <t>کارشناسان سیتوژنتیک | سیتوتکنولوژیست‌ها / کارشناسان سیتولوژی | هیستوتکنولوژیست‌ها / کارشناسان بافت‌شناسی | پژوهشگران و دانشمندان علوم پزشکی | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان علوم آزمایشگاهی بالینی | متخصصان رادیولوژی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,12 +736,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | نگارش | یادگیری فعال | نظارت | علوم پایه | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | نگارش | یادگیری فعال | نظارت | علوم | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>درمان و مشاوره | روان‌شناسی | پزشکی و دندانپزشکی | زیست‌شناسی | آموزش و تدریس | جامعه‌شناسی و مردم‌شناسی</t>
+          <t>درمان و مشاوره | روان‌شناسی | پزشکی و دندان‌پزشکی | زیست‌شناسی | آموزش و پرورش | جامعه‌شناسی و انسان‌شناسی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>پرستاران پیشرفته روان‌پزشکی | متخصصان روان‌شناسی اعصاب بالینی | روان‌شناسان بالینی و مشاوره | پزشکان خانواده | متخصصان مغز و اعصاب | متخصصان عمومی کودکان | تکنسین‌های روان‌پزشکی</t>
+          <t>پرستاران تخصصی روانپزشکی | متخصصان عصب‌روان‌شناسی بالینی | روان‌شناسان بالینی و مشاوران سلامت روان | پزشکان عمومی و خانواده | متخصصان مغز و اعصاب | متخصصان عمومی کودکان | تکنسین‌های روان‌پزشکی و بهداشت روان</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | نگارش | تفکر انتقادی | نظارت | یادگیری فعال | علوم پایه | راهبردهای یادگیری</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | تفکر انتقادی | نظارت | یادگیری فعال | علوم | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | زبان انگلیسی | رایانه و الکترونیک | آموزش و تدریس | خدمات مشتریان و خدمات فردی | فیزیک</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | زبان انگلیسی | رایانه و الکترونیک | آموزش و پرورش | خدمات مشتری و شخصی | فیزیک</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>استدلال استقرایی | حساسیت به مسئله | بیان شفاهی | درک شفاهی | درک کتبی | استدلال قیاسی | دید نزدیک</t>
+          <t>استدلال استقرایی | حساسیت به مسئله | بیان شفاهی | درک شفاهی | درک کتبی | استدلال قیاسی | بینایی نزدیک</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>کارشناسان و تکنسین‌های قلب و عروق | کارشناسان سونوگرافی تشخیصی | کارشناسان فناوری تشخیص اعصاب | کارشناسان طب هسته‌ای | پزشکان متخصص پاتولوژی | کارشناسان پرتودرمانی (رادیوتراپی) | کارشناسان و تکنسین‌های رادیولوژی</t>
+          <t>کارشناسان و تکنسین‌های قلب و عروق | سونوگرافیست‌های تشخیصی / کارشناسان سونوگرافی | تکنسین‌های الکترونورودیاگنوستیک | کارشناسان و تکنسین‌های پزشکی هسته‌ای | پزشکان متخصص پاتولوژی | پرتودرمانگران / کارشناسان رادیوتراپی | کارشناسان و تکنسین‌های رادیولوژی و پرتونگاری</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,12 +850,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | سخن گفتن | علوم پایه | نظارت | یادگیری فعال | نگارش</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | علوم | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | شیمی | روان‌شناسی | خدمات مشتریان و خدمات فردی | درمان و مشاوره</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | شیمی | روان‌شناسی | خدمات مشتری و شخصی | درمان و مشاوره</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>پزشکان خانواده | متخصصان بیماری‌های داخلی | پزشکان طب اورژانس | متخصصان عمومی کودکان | روان‌پزشکان | متخصصان بیهوشی | جراحان، سایر تخصص‌ها</t>
+          <t>پزشکان عمومی و خانواده | پزشکان متخصص بیماری‌های داخلی | پزشکان طب اورژانس | متخصصان عمومی کودکان | روان‌پزشکان | متخصصان بیهوشی | سایر جراحان</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,12 +907,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب | نگارش | تفکر انتقادی | شنیدن فعال | سخن گفتن | نظارت | یادگیری فعال | علوم پایه | راهبردهای یادگیری</t>
+          <t>درک مطلب | نگارش | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نظارت | یادگیری فعال | علوم | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | خدمات مشتریان و خدمات فردی | زیست‌شناسی | مدیریت و امور اداری | آموزش و تدریس | شیمی</t>
+          <t>پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی | زیست‌شناسی | مدیریت و اداره | آموزش و پرورش | شیمی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>متخصصان پوست و مو | پزشکان طب اورژانس | پزشکان خانواده | متخصصان بیماری‌های داخلی | متخصصان مغز و اعصاب | متخصصان عمومی کودکان | پزشکان متخصص پاتولوژی</t>
+          <t>متخصصان پوست و مو | پزشکان طب اورژانس | پزشکان عمومی و خانواده | پزشکان متخصص بیماری‌های داخلی | متخصصان مغز و اعصاب | متخصصان عمومی کودکان | پزشکان متخصص پاتولوژی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,12 +964,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | سخن گفتن | تفکر انتقادی | یادگیری فعال | نظارت | نگارش | علوم پایه | راهبردهای یادگیری | ریاضیات</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی | یادگیری فعال | نظارت | نگارش | علوم | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | روان‌شناسی | آموزش و تدریس | درمان و مشاوره | مدیریت و امور اداری</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | روان‌شناسی | آموزش و پرورش | درمان و مشاوره | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های حاد | پرستاران مراقبت‌های ویژه (ICU) | پزشکان طب اورژانس | پزشکان خانواده | متخصصان بیماری‌های داخلی | دستیاران پزشک | پرستاران رسمی</t>
+          <t>پرستاران مراقبت‌های حاد | پرستاران مراقبت‌های ویژه | پزشکان طب اورژانس | پزشکان عمومی و خانواده | پزشکان متخصص بیماری‌های داخلی | دستیاران پزشک | پرستاران</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,12 +1021,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | نگارش | سخن گفتن | یادگیری فعال | نظارت | علوم پایه | راهبردهای یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | نگارش | سخن گفتن | یادگیری فعال | نظارت | علوم | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | آموزش و تدریس | درمان و مشاوره | روان‌شناسی | شیمی</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | آموزش و پرورش | درمان و مشاوره | روان‌شناسی | شیمی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>متخصصان بیهوشی | پزشکان خانواده | متخصصان بیماری‌های داخلی | متخصصان زنان و زایمان | جراحان ارتوپدی، غیر از کودکان | دستیاران پزشک | متخصصان رادیولوژی</t>
+          <t>متخصصان بیهوشی | پزشکان عمومی و خانواده | پزشکان متخصص بیماری‌های داخلی | متخصصان زنان و زایمان | جراحان ارتوپدی، غیر از اطفال | دستیاران پزشک | متخصصان رادیولوژی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
